--- a/base_datos_taller.xlsx
+++ b/base_datos_taller.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2700160f2e68de60/Desktop/entrega proyecto final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2700160f2e68de60/Desktop/Repositorios githup/entrega-proyecto-final-de-curso/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{0B06429E-908F-45A8-BF0A-A27AC1131541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{546CD4E0-1765-4D07-876F-5AA56F326B9C}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{0B06429E-908F-45A8-BF0A-A27AC1131541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00176F26-B61C-436A-A3A6-3F44F6E2A2BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87F78E75-C6CA-483E-9B8B-8416EF509633}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20018" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20018" uniqueCount="130">
   <si>
     <t>id_boleta</t>
   </si>
@@ -389,6 +389,33 @@
   <si>
     <t>174/2/2026</t>
   </si>
+  <si>
+    <t>palio</t>
+  </si>
+  <si>
+    <t>cld-009</t>
+  </si>
+  <si>
+    <t>celerio</t>
+  </si>
+  <si>
+    <t>focus</t>
+  </si>
+  <si>
+    <t>subaru</t>
+  </si>
+  <si>
+    <t>wrx</t>
+  </si>
+  <si>
+    <t>s-200</t>
+  </si>
+  <si>
+    <t>aveo</t>
+  </si>
+  <si>
+    <t>explorer</t>
+  </si>
 </sst>
 </file>
 
@@ -426,12 +453,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2122,7 +2148,7 @@
         <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="F29" s="3">
         <v>2001</v>
@@ -3274,7 +3300,7 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="F53" s="3">
         <v>2021</v>
@@ -3283,14 +3309,14 @@
         <v>21</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I53" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J53" t="str">
         <f t="shared" ref="J53:J79" si="1">IF(H53="Optimo", "Cat A - Garantizado", IF(H53="Dañado - Decide Reparar", "Cat B - Reparacion", IF(H53="Dañado - Acepta Sin Garantia", "Cat C - Sin Garantia", "")))</f>
-        <v>Cat A - Garantizado</v>
+        <v>Cat B - Reparacion</v>
       </c>
       <c r="K53" t="s">
         <v>17</v>
@@ -3305,7 +3331,7 @@
         <v>19</v>
       </c>
       <c r="O53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -10666,23 +10692,23 @@
         <v>103</v>
       </c>
       <c r="E207" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="F207" s="3">
         <v>2009</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H207" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I207" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J207" t="str">
         <f t="shared" si="6"/>
-        <v>Cat A - Garantizado</v>
+        <v>Cat C - Sin Garantia</v>
       </c>
       <c r="K207" t="s">
         <v>17</v>
@@ -10697,7 +10723,7 @@
         <v>28</v>
       </c>
       <c r="O207" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
@@ -35106,7 +35132,7 @@
       <c r="G716" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H716" s="4" t="s">
+      <c r="H716" t="s">
         <v>14</v>
       </c>
       <c r="I716" s="3">
@@ -40147,14 +40173,14 @@
         <v>32</v>
       </c>
       <c r="H821" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I821" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J821" t="str">
         <f t="shared" si="26"/>
-        <v>Cat A - Garantizado</v>
+        <v>Cat C - Sin Garantia</v>
       </c>
       <c r="K821" t="s">
         <v>17</v>
@@ -40169,7 +40195,7 @@
         <v>19</v>
       </c>
       <c r="O821" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="822" spans="1:15" x14ac:dyDescent="0.25">
@@ -43252,13 +43278,13 @@
         <v>46073</v>
       </c>
       <c r="C886" s="2" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="D886" t="s">
         <v>79</v>
       </c>
       <c r="E886" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="F886" s="3">
         <v>2006</v>
@@ -43267,14 +43293,14 @@
         <v>21</v>
       </c>
       <c r="H886" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I886" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J886" t="str">
         <f t="shared" si="28"/>
-        <v>Cat A - Garantizado</v>
+        <v>Cat C - Sin Garantia</v>
       </c>
       <c r="K886" t="s">
         <v>18</v>
@@ -43289,7 +43315,7 @@
         <v>19</v>
       </c>
       <c r="O886" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="887" spans="1:15" x14ac:dyDescent="0.25">
@@ -43978,23 +44004,23 @@
         <v>73</v>
       </c>
       <c r="E901" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="F901" s="3">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="G901" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H901" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I901" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J901" t="str">
         <f t="shared" si="28"/>
-        <v>Cat A - Garantizado</v>
+        <v>Cat C - Sin Garantia</v>
       </c>
       <c r="K901" t="s">
         <v>17</v>
@@ -44009,7 +44035,7 @@
         <v>19</v>
       </c>
       <c r="O901" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="902" spans="1:15" x14ac:dyDescent="0.25">
@@ -46243,14 +46269,14 @@
         <v>21</v>
       </c>
       <c r="H948" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I948" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J948" t="str">
         <f t="shared" si="30"/>
-        <v>Cat A - Garantizado</v>
+        <v>Cat C - Sin Garantia</v>
       </c>
       <c r="K948" t="s">
         <v>17</v>
@@ -46265,7 +46291,7 @@
         <v>28</v>
       </c>
       <c r="O948" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="949" spans="1:15" x14ac:dyDescent="0.25">
@@ -51178,7 +51204,7 @@
         <v>103</v>
       </c>
       <c r="E1051" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="F1051" s="3">
         <v>2009</v>
@@ -51187,14 +51213,14 @@
         <v>21</v>
       </c>
       <c r="H1051" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I1051" s="3">
         <v>20</v>
       </c>
       <c r="J1051" t="str">
         <f t="shared" si="32"/>
-        <v>Cat A - Garantizado</v>
+        <v>Cat C - Sin Garantia</v>
       </c>
       <c r="K1051" t="s">
         <v>17</v>
@@ -51209,7 +51235,7 @@
         <v>28</v>
       </c>
       <c r="O1051" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1052" spans="1:15" x14ac:dyDescent="0.25">
@@ -54967,10 +54993,10 @@
         <v>85</v>
       </c>
       <c r="D1130" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="E1130" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="F1130" s="3">
         <v>2013</v>
